--- a/SEMB_ERP/wwwroot/Upload/Template_Upload_Material (1).xlsx
+++ b/SEMB_ERP/wwwroot/Upload/Template_Upload_Material (1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SESA546923\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SESA546923\Documents\GitHub\SEMB_ERP\SEMB_ERP\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D259BF59-FE99-4854-8414-0CB8B0A6E192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6E36C8-6B46-428A-80AF-2F4228AC54B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{610016C1-593C-4B28-8FE2-E321024077D0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{610016C1-593C-4B28-8FE2-E321024077D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>Material Type</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Remark</t>
   </si>
   <si>
-    <t>RAW</t>
-  </si>
-  <si>
     <t>FG</t>
   </si>
   <si>
@@ -270,22 +267,7 @@
     <t>Height (mm)</t>
   </si>
   <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>Apolo</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>ABCDE</t>
-  </si>
-  <si>
-    <t>AB</t>
-  </si>
-  <si>
-    <t>Supplier B</t>
+    <t>RM</t>
   </si>
 </sst>
 </file>
@@ -655,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AAC486F-9B95-4840-90FB-639F5A25D6B8}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -677,46 +659,46 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>20</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>24</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>26</v>
       </c>
-      <c r="K1" t="s">
-        <v>27</v>
-      </c>
       <c r="L1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s">
         <v>30</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>31</v>
-      </c>
-      <c r="N1" t="s">
-        <v>32</v>
       </c>
       <c r="O1" t="s">
         <v>3</v>
@@ -724,34 +706,34 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
       <c r="J2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2">
         <v>10.5</v>
@@ -771,34 +753,34 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D3">
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
       <c r="J3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3">
         <v>5.5</v>
@@ -813,35 +795,6 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4">
-        <v>12</v>
-      </c>
-      <c r="O4" t="s">
         <v>3</v>
       </c>
     </row>
@@ -857,19 +810,19 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A3 A5:A1048576</xm:sqref>
+          <xm:sqref>A2:A1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{901A8E3A-F7A9-4682-9610-BD38C193DED9}">
+          <x14:formula1>
+            <xm:f>Sheet2!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C664FC6C-39F8-4E81-8AC0-2672C0A59989}">
           <x14:formula1>
             <xm:f>Sheet2!$E$2:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J3 J5:J1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{901A8E3A-F7A9-4682-9610-BD38C193DED9}">
-          <x14:formula1>
-            <xm:f>Sheet2!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>H2:H3 H5:H1048576</xm:sqref>
+          <xm:sqref>J2:J1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -899,32 +852,32 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
